--- a/client/public/templates/bracket_players/8-player.xlsx
+++ b/client/public/templates/bracket_players/8-player.xlsx
@@ -5,17 +5,17 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bellahuang/Downloads/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/bellahuang/Downloads/Players/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{1AEA630C-815E-5F47-9854-AD64DCDBBA9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BE3C2744-6067-2441-9F97-BC49A7F0217D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="820" windowWidth="34200" windowHeight="21360" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Poster" sheetId="1" r:id="rId1"/>
-    <sheet name="Booklet (left)" sheetId="2" r:id="rId2"/>
-    <sheet name="Booklet (right)" sheetId="3" r:id="rId3"/>
+    <sheet name="Full" sheetId="1" r:id="rId1"/>
+    <sheet name="Left" sheetId="2" r:id="rId2"/>
+    <sheet name="Right" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
@@ -356,37 +356,37 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -396,11 +396,11 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -834,8 +834,8 @@
       <c r="V3" s="4"/>
     </row>
     <row r="4" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A4" s="51"/>
-      <c r="B4" s="52"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="55"/>
       <c r="C4" s="5"/>
       <c r="D4" s="4"/>
       <c r="E4" s="4"/>
@@ -858,8 +858,8 @@
       <c r="V4" s="4"/>
     </row>
     <row r="5" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A5" s="46"/>
-      <c r="B5" s="48"/>
+      <c r="A5" s="48"/>
+      <c r="B5" s="50"/>
       <c r="C5" s="6"/>
       <c r="D5" s="7"/>
       <c r="E5" s="4"/>
@@ -878,14 +878,14 @@
       <c r="V5" s="4"/>
     </row>
     <row r="6" spans="1:22" ht="16" customHeight="1">
-      <c r="A6" s="53"/>
-      <c r="B6" s="50"/>
-      <c r="C6" s="49">
+      <c r="A6" s="57"/>
+      <c r="B6" s="46"/>
+      <c r="C6" s="54">
         <v>1</v>
       </c>
       <c r="D6" s="9"/>
-      <c r="E6" s="51"/>
-      <c r="F6" s="52"/>
+      <c r="E6" s="56"/>
+      <c r="F6" s="55"/>
       <c r="G6" s="5"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -902,10 +902,10 @@
     <row r="7" spans="1:22" ht="15.75" customHeight="1">
       <c r="A7" s="5"/>
       <c r="B7" s="4"/>
-      <c r="C7" s="50"/>
+      <c r="C7" s="46"/>
       <c r="D7" s="10"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="11"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -924,8 +924,8 @@
       <c r="V7" s="4"/>
     </row>
     <row r="8" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A8" s="54"/>
-      <c r="B8" s="47"/>
+      <c r="A8" s="47"/>
+      <c r="B8" s="49"/>
       <c r="C8" s="12"/>
       <c r="D8" s="4"/>
       <c r="E8" s="4"/>
@@ -943,8 +943,8 @@
       <c r="V8" s="4"/>
     </row>
     <row r="9" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A9" s="46"/>
-      <c r="B9" s="48"/>
+      <c r="A9" s="48"/>
+      <c r="B9" s="50"/>
       <c r="C9" s="14"/>
       <c r="D9" s="4"/>
       <c r="E9" s="4"/>
@@ -962,18 +962,18 @@
       <c r="V9" s="4"/>
     </row>
     <row r="10" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A10" s="55"/>
-      <c r="B10" s="50"/>
+      <c r="A10" s="51"/>
+      <c r="B10" s="46"/>
       <c r="C10" s="5"/>
       <c r="D10" s="4"/>
       <c r="E10" s="4"/>
       <c r="F10" s="4"/>
-      <c r="G10" s="49">
+      <c r="G10" s="54">
         <v>5</v>
       </c>
       <c r="H10" s="9"/>
-      <c r="I10" s="51"/>
-      <c r="J10" s="52"/>
+      <c r="I10" s="56"/>
+      <c r="J10" s="55"/>
       <c r="K10" s="4"/>
       <c r="M10" s="4"/>
       <c r="N10" s="4"/>
@@ -993,10 +993,10 @@
       <c r="D11" s="4"/>
       <c r="E11" s="4"/>
       <c r="F11" s="4"/>
-      <c r="G11" s="50"/>
+      <c r="G11" s="46"/>
       <c r="H11" s="10"/>
-      <c r="I11" s="46"/>
-      <c r="J11" s="48"/>
+      <c r="I11" s="48"/>
+      <c r="J11" s="50"/>
       <c r="K11" s="16"/>
       <c r="L11" s="7"/>
       <c r="M11" s="4"/>
@@ -1031,8 +1031,8 @@
       <c r="V12" s="4"/>
     </row>
     <row r="13" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A13" s="54"/>
-      <c r="B13" s="47"/>
+      <c r="A13" s="47"/>
+      <c r="B13" s="49"/>
       <c r="C13" s="5"/>
       <c r="D13" s="4"/>
       <c r="E13" s="4"/>
@@ -1055,8 +1055,8 @@
       <c r="V13" s="4"/>
     </row>
     <row r="14" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A14" s="46"/>
-      <c r="B14" s="48"/>
+      <c r="A14" s="48"/>
+      <c r="B14" s="50"/>
       <c r="C14" s="6"/>
       <c r="D14" s="7"/>
       <c r="E14" s="4"/>
@@ -1079,14 +1079,14 @@
       <c r="V14" s="4"/>
     </row>
     <row r="15" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A15" s="56"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="49">
+      <c r="A15" s="52"/>
+      <c r="B15" s="46"/>
+      <c r="C15" s="54">
         <v>2</v>
       </c>
       <c r="D15" s="9"/>
-      <c r="E15" s="45"/>
-      <c r="F15" s="47"/>
+      <c r="E15" s="53"/>
+      <c r="F15" s="49"/>
       <c r="G15" s="18"/>
       <c r="H15" s="7"/>
       <c r="I15" s="4"/>
@@ -1107,10 +1107,10 @@
     <row r="16" spans="1:22" ht="15.75" customHeight="1">
       <c r="A16" s="5"/>
       <c r="B16" s="4"/>
-      <c r="C16" s="50"/>
+      <c r="C16" s="46"/>
       <c r="D16" s="10"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="50"/>
       <c r="G16" s="5"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -1129,8 +1129,8 @@
       <c r="V16" s="4"/>
     </row>
     <row r="17" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A17" s="54"/>
-      <c r="B17" s="47"/>
+      <c r="A17" s="47"/>
+      <c r="B17" s="49"/>
       <c r="C17" s="19"/>
       <c r="D17" s="4"/>
       <c r="E17" s="4"/>
@@ -1153,8 +1153,8 @@
       <c r="V17" s="4"/>
     </row>
     <row r="18" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A18" s="46"/>
-      <c r="B18" s="48"/>
+      <c r="A18" s="48"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="6"/>
       <c r="D18" s="4"/>
       <c r="E18" s="4"/>
@@ -1177,8 +1177,8 @@
       <c r="V18" s="4"/>
     </row>
     <row r="19" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A19" s="55"/>
-      <c r="B19" s="50"/>
+      <c r="A19" s="51"/>
+      <c r="B19" s="46"/>
       <c r="C19" s="5"/>
       <c r="D19" s="4"/>
       <c r="E19" s="4"/>
@@ -1208,12 +1208,12 @@
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
       <c r="J20" s="4"/>
-      <c r="K20" s="49">
+      <c r="K20" s="54">
         <v>7</v>
       </c>
       <c r="L20" s="9"/>
-      <c r="M20" s="51"/>
-      <c r="N20" s="52"/>
+      <c r="M20" s="56"/>
+      <c r="N20" s="55"/>
       <c r="O20" s="4"/>
       <c r="P20" s="4"/>
       <c r="Q20" s="4"/>
@@ -1231,10 +1231,10 @@
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
       <c r="J21" s="4"/>
-      <c r="K21" s="50"/>
+      <c r="K21" s="46"/>
       <c r="L21" s="10"/>
-      <c r="M21" s="46"/>
-      <c r="N21" s="48"/>
+      <c r="M21" s="48"/>
+      <c r="N21" s="50"/>
       <c r="O21" s="4"/>
       <c r="P21" s="4"/>
       <c r="Q21" s="4"/>
@@ -1245,8 +1245,8 @@
       <c r="V21" s="4"/>
     </row>
     <row r="22" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A22" s="54"/>
-      <c r="B22" s="47"/>
+      <c r="A22" s="47"/>
+      <c r="B22" s="49"/>
       <c r="C22" s="5"/>
       <c r="D22" s="4"/>
       <c r="E22" s="4"/>
@@ -1266,8 +1266,8 @@
       <c r="V22" s="4"/>
     </row>
     <row r="23" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A23" s="46"/>
-      <c r="B23" s="48"/>
+      <c r="A23" s="48"/>
+      <c r="B23" s="50"/>
       <c r="C23" s="6"/>
       <c r="D23" s="7"/>
       <c r="E23" s="4"/>
@@ -1289,14 +1289,14 @@
       <c r="V23" s="4"/>
     </row>
     <row r="24" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A24" s="56"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="49">
+      <c r="A24" s="52"/>
+      <c r="B24" s="46"/>
+      <c r="C24" s="54">
         <v>3</v>
       </c>
       <c r="D24" s="9"/>
-      <c r="E24" s="45"/>
-      <c r="F24" s="47"/>
+      <c r="E24" s="53"/>
+      <c r="F24" s="49"/>
       <c r="G24" s="5"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -1314,10 +1314,10 @@
     <row r="25" spans="1:22" ht="15.75" customHeight="1">
       <c r="A25" s="5"/>
       <c r="B25" s="4"/>
-      <c r="C25" s="50"/>
+      <c r="C25" s="46"/>
       <c r="D25" s="10"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="50"/>
       <c r="G25" s="11"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -1334,8 +1334,8 @@
       <c r="V25" s="4"/>
     </row>
     <row r="26" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A26" s="54"/>
-      <c r="B26" s="47"/>
+      <c r="A26" s="47"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="13"/>
       <c r="G26" s="13"/>
       <c r="K26" s="4"/>
@@ -1352,8 +1352,8 @@
       <c r="V26" s="4"/>
     </row>
     <row r="27" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A27" s="46"/>
-      <c r="B27" s="48"/>
+      <c r="A27" s="48"/>
+      <c r="B27" s="50"/>
       <c r="C27" s="6"/>
       <c r="G27" s="13"/>
       <c r="K27" s="4"/>
@@ -1368,8 +1368,8 @@
       <c r="V27" s="4"/>
     </row>
     <row r="28" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A28" s="55"/>
-      <c r="B28" s="50"/>
+      <c r="A28" s="51"/>
+      <c r="B28" s="46"/>
       <c r="C28" s="5"/>
       <c r="D28" s="4"/>
       <c r="E28" s="4"/>
@@ -1392,12 +1392,12 @@
       <c r="D29" s="4"/>
       <c r="E29" s="4"/>
       <c r="F29" s="4"/>
-      <c r="G29" s="49">
+      <c r="G29" s="54">
         <v>6</v>
       </c>
       <c r="H29" s="9"/>
-      <c r="I29" s="45"/>
-      <c r="J29" s="47"/>
+      <c r="I29" s="53"/>
+      <c r="J29" s="49"/>
       <c r="K29" s="4"/>
       <c r="L29" s="7"/>
       <c r="M29" s="4"/>
@@ -1415,10 +1415,10 @@
       <c r="D30" s="4"/>
       <c r="E30" s="4"/>
       <c r="F30" s="4"/>
-      <c r="G30" s="50"/>
+      <c r="G30" s="46"/>
       <c r="H30" s="10"/>
-      <c r="I30" s="46"/>
-      <c r="J30" s="48"/>
+      <c r="I30" s="48"/>
+      <c r="J30" s="50"/>
       <c r="K30" s="16"/>
       <c r="L30" s="4"/>
       <c r="M30" s="4"/>
@@ -1433,8 +1433,8 @@
       <c r="V30" s="4"/>
     </row>
     <row r="31" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A31" s="54"/>
-      <c r="B31" s="47"/>
+      <c r="A31" s="47"/>
+      <c r="B31" s="49"/>
       <c r="C31" s="5"/>
       <c r="D31" s="4"/>
       <c r="E31" s="4"/>
@@ -1452,8 +1452,8 @@
       <c r="V31" s="4"/>
     </row>
     <row r="32" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A32" s="46"/>
-      <c r="B32" s="48"/>
+      <c r="A32" s="48"/>
+      <c r="B32" s="50"/>
       <c r="C32" s="6"/>
       <c r="D32" s="7"/>
       <c r="E32" s="4"/>
@@ -1474,14 +1474,14 @@
       <c r="V32" s="4"/>
     </row>
     <row r="33" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A33" s="56"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="49">
+      <c r="A33" s="52"/>
+      <c r="B33" s="46"/>
+      <c r="C33" s="54">
         <v>4</v>
       </c>
       <c r="D33" s="9"/>
-      <c r="E33" s="45"/>
-      <c r="F33" s="47"/>
+      <c r="E33" s="53"/>
+      <c r="F33" s="49"/>
       <c r="G33" s="12"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -1501,10 +1501,10 @@
     <row r="34" spans="1:22" ht="15.75" customHeight="1">
       <c r="A34" s="5"/>
       <c r="B34" s="4"/>
-      <c r="C34" s="50"/>
+      <c r="C34" s="46"/>
       <c r="D34" s="10"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="50"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
       <c r="J34" s="4"/>
@@ -1522,8 +1522,8 @@
       <c r="V34" s="4"/>
     </row>
     <row r="35" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A35" s="54"/>
-      <c r="B35" s="47"/>
+      <c r="A35" s="47"/>
+      <c r="B35" s="49"/>
       <c r="C35" s="19"/>
       <c r="D35" s="7"/>
       <c r="E35" s="4"/>
@@ -1546,8 +1546,8 @@
       <c r="V35" s="4"/>
     </row>
     <row r="36" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A36" s="46"/>
-      <c r="B36" s="48"/>
+      <c r="A36" s="48"/>
+      <c r="B36" s="50"/>
       <c r="C36" s="6"/>
       <c r="D36" s="4"/>
       <c r="E36" s="4"/>
@@ -1570,8 +1570,8 @@
       <c r="V36" s="4"/>
     </row>
     <row r="37" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A37" s="55"/>
-      <c r="B37" s="50"/>
+      <c r="A37" s="51"/>
+      <c r="B37" s="46"/>
       <c r="K37" s="4"/>
       <c r="L37" s="4"/>
       <c r="M37" s="4"/>
@@ -1586,8 +1586,8 @@
       <c r="V37" s="4"/>
     </row>
     <row r="38" spans="1:22" ht="16">
-      <c r="A38" s="57"/>
-      <c r="B38" s="50"/>
+      <c r="A38" s="45"/>
+      <c r="B38" s="46"/>
       <c r="C38" s="5"/>
       <c r="D38" s="4"/>
       <c r="E38" s="4"/>
@@ -24549,19 +24549,23 @@
     </row>
   </sheetData>
   <mergeCells count="46">
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="B26:B27"/>
-    <mergeCell ref="A28:B28"/>
-    <mergeCell ref="A31:A32"/>
-    <mergeCell ref="B31:B32"/>
-    <mergeCell ref="A33:B33"/>
-    <mergeCell ref="E33:E34"/>
-    <mergeCell ref="F33:F34"/>
-    <mergeCell ref="A35:A36"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="I10:I11"/>
+    <mergeCell ref="J10:J11"/>
+    <mergeCell ref="K20:K21"/>
+    <mergeCell ref="M20:M21"/>
+    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="A4:A5"/>
+    <mergeCell ref="B4:B5"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="C6:C7"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F15:F16"/>
+    <mergeCell ref="G10:G11"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="A8:A9"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A10:B10"/>
+    <mergeCell ref="B13:B14"/>
     <mergeCell ref="J29:J30"/>
     <mergeCell ref="A13:A14"/>
     <mergeCell ref="A17:A18"/>
@@ -24578,23 +24582,19 @@
     <mergeCell ref="A15:B15"/>
     <mergeCell ref="C15:C16"/>
     <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="G10:G11"/>
-    <mergeCell ref="F6:F7"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="A10:B10"/>
-    <mergeCell ref="B13:B14"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:C7"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="I10:I11"/>
-    <mergeCell ref="J10:J11"/>
-    <mergeCell ref="K20:K21"/>
-    <mergeCell ref="M20:M21"/>
-    <mergeCell ref="N20:N21"/>
+    <mergeCell ref="E33:E34"/>
+    <mergeCell ref="F33:F34"/>
+    <mergeCell ref="A35:A36"/>
+    <mergeCell ref="B35:B36"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="C33:C34"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="B26:B27"/>
+    <mergeCell ref="A28:B28"/>
+    <mergeCell ref="A31:A32"/>
+    <mergeCell ref="B31:B32"/>
+    <mergeCell ref="A33:B33"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -24636,8 +24636,8 @@
       <c r="R1" s="4"/>
     </row>
     <row r="2" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A2" s="58"/>
-      <c r="B2" s="59"/>
+      <c r="A2" s="63"/>
+      <c r="B2" s="64"/>
       <c r="C2" s="21"/>
       <c r="D2" s="22"/>
       <c r="E2" s="21"/>
@@ -24655,8 +24655,8 @@
       <c r="R2" s="4"/>
     </row>
     <row r="3" spans="1:18" ht="16">
-      <c r="A3" s="46"/>
-      <c r="B3" s="48"/>
+      <c r="A3" s="48"/>
+      <c r="B3" s="50"/>
       <c r="C3" s="23"/>
       <c r="D3" s="24"/>
       <c r="E3" s="21"/>
@@ -24709,7 +24709,7 @@
     </row>
     <row r="6" spans="1:18" ht="16">
       <c r="A6" s="62"/>
-      <c r="B6" s="63"/>
+      <c r="B6" s="59"/>
       <c r="C6" s="30"/>
       <c r="D6" s="31"/>
       <c r="E6" s="25"/>
@@ -24726,8 +24726,8 @@
       <c r="R6" s="4"/>
     </row>
     <row r="7" spans="1:18" ht="16">
-      <c r="A7" s="46"/>
-      <c r="B7" s="48"/>
+      <c r="A7" s="48"/>
+      <c r="B7" s="50"/>
       <c r="C7" s="32"/>
       <c r="D7" s="31"/>
       <c r="E7" s="25"/>
@@ -24801,7 +24801,7 @@
     </row>
     <row r="11" spans="1:18" ht="16">
       <c r="A11" s="62"/>
-      <c r="B11" s="63"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="21"/>
       <c r="D11" s="27"/>
       <c r="E11" s="22"/>
@@ -24818,8 +24818,8 @@
       <c r="R11" s="4"/>
     </row>
     <row r="12" spans="1:18" ht="16">
-      <c r="A12" s="46"/>
-      <c r="B12" s="48"/>
+      <c r="A12" s="48"/>
+      <c r="B12" s="50"/>
       <c r="C12" s="29"/>
       <c r="D12" s="27"/>
       <c r="E12" s="22"/>
@@ -24875,7 +24875,7 @@
     </row>
     <row r="15" spans="1:18" ht="16">
       <c r="A15" s="62"/>
-      <c r="B15" s="63"/>
+      <c r="B15" s="59"/>
       <c r="C15" s="27"/>
       <c r="D15" s="21"/>
       <c r="E15" s="22"/>
@@ -24892,8 +24892,8 @@
       <c r="R15" s="4"/>
     </row>
     <row r="16" spans="1:18" ht="16">
-      <c r="A16" s="46"/>
-      <c r="B16" s="48"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="50"/>
       <c r="C16" s="23"/>
       <c r="D16" s="21"/>
       <c r="E16" s="22"/>
@@ -24931,7 +24931,7 @@
       <c r="B18" s="20"/>
       <c r="C18" s="25"/>
       <c r="D18" s="21"/>
-      <c r="E18" s="64">
+      <c r="E18" s="58">
         <v>7</v>
       </c>
       <c r="F18" s="28"/>
@@ -24950,7 +24950,7 @@
       <c r="B19" s="20"/>
       <c r="C19" s="25"/>
       <c r="D19" s="21"/>
-      <c r="E19" s="50"/>
+      <c r="E19" s="46"/>
       <c r="F19" s="35"/>
       <c r="G19" s="25"/>
       <c r="J19" s="2"/>
@@ -24965,7 +24965,7 @@
     </row>
     <row r="20" spans="1:18" ht="16">
       <c r="A20" s="62"/>
-      <c r="B20" s="63"/>
+      <c r="B20" s="59"/>
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
       <c r="E20" s="31"/>
@@ -24980,8 +24980,8 @@
       <c r="R20" s="4"/>
     </row>
     <row r="21" spans="1:18" ht="16">
-      <c r="A21" s="46"/>
-      <c r="B21" s="48"/>
+      <c r="A21" s="48"/>
+      <c r="B21" s="50"/>
       <c r="C21" s="29"/>
       <c r="D21" s="21"/>
       <c r="E21" s="31"/>
@@ -25033,7 +25033,7 @@
     </row>
     <row r="24" spans="1:18" ht="16">
       <c r="A24" s="62"/>
-      <c r="B24" s="63"/>
+      <c r="B24" s="59"/>
       <c r="C24" s="31"/>
       <c r="D24" s="31"/>
       <c r="E24" s="22"/>
@@ -25050,8 +25050,8 @@
       <c r="R24" s="4"/>
     </row>
     <row r="25" spans="1:18" ht="16">
-      <c r="A25" s="46"/>
-      <c r="B25" s="48"/>
+      <c r="A25" s="48"/>
+      <c r="B25" s="50"/>
       <c r="C25" s="23"/>
       <c r="D25" s="31"/>
       <c r="E25" s="22"/>
@@ -25121,7 +25121,7 @@
     </row>
     <row r="29" spans="1:18" ht="16">
       <c r="A29" s="62"/>
-      <c r="B29" s="63"/>
+      <c r="B29" s="59"/>
       <c r="C29" s="21"/>
       <c r="D29" s="27"/>
       <c r="E29" s="25"/>
@@ -25138,8 +25138,8 @@
       <c r="R29" s="4"/>
     </row>
     <row r="30" spans="1:18" ht="16">
-      <c r="A30" s="46"/>
-      <c r="B30" s="48"/>
+      <c r="A30" s="48"/>
+      <c r="B30" s="50"/>
       <c r="C30" s="29"/>
       <c r="D30" s="27"/>
       <c r="E30" s="25"/>
@@ -25196,7 +25196,7 @@
     </row>
     <row r="33" spans="1:18" ht="15.75" customHeight="1">
       <c r="A33" s="62"/>
-      <c r="B33" s="63"/>
+      <c r="B33" s="59"/>
       <c r="C33" s="27"/>
       <c r="D33" s="24"/>
       <c r="E33" s="21"/>
@@ -25214,8 +25214,8 @@
       <c r="R33" s="4"/>
     </row>
     <row r="34" spans="1:18" ht="15.75" customHeight="1">
-      <c r="A34" s="46"/>
-      <c r="B34" s="48"/>
+      <c r="A34" s="48"/>
+      <c r="B34" s="50"/>
       <c r="C34" s="23"/>
       <c r="D34" s="22"/>
       <c r="E34" s="21"/>
@@ -42923,6 +42923,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="A2:A3"/>
+    <mergeCell ref="B2:B3"/>
+    <mergeCell ref="C4:C5"/>
+    <mergeCell ref="A6:A7"/>
+    <mergeCell ref="B6:B7"/>
+    <mergeCell ref="D8:D9"/>
+    <mergeCell ref="A11:A12"/>
+    <mergeCell ref="B11:B12"/>
+    <mergeCell ref="C13:C14"/>
+    <mergeCell ref="A15:A16"/>
+    <mergeCell ref="B15:B16"/>
     <mergeCell ref="E18:E19"/>
     <mergeCell ref="B20:B21"/>
     <mergeCell ref="C22:C23"/>
@@ -42935,17 +42946,6 @@
     <mergeCell ref="A29:A30"/>
     <mergeCell ref="B29:B30"/>
     <mergeCell ref="C31:C32"/>
-    <mergeCell ref="D8:D9"/>
-    <mergeCell ref="A11:A12"/>
-    <mergeCell ref="B11:B12"/>
-    <mergeCell ref="C13:C14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:B16"/>
-    <mergeCell ref="A2:A3"/>
-    <mergeCell ref="B2:B3"/>
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B6:B7"/>
   </mergeCells>
   <printOptions horizontalCentered="1" gridLines="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
@@ -42986,8 +42986,8 @@
       <c r="B2" s="21"/>
       <c r="C2" s="22"/>
       <c r="D2" s="21"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="59"/>
+      <c r="E2" s="63"/>
+      <c r="F2" s="64"/>
       <c r="G2" s="4"/>
       <c r="H2" s="4"/>
       <c r="I2" s="4"/>
@@ -43001,8 +43001,8 @@
       <c r="B3" s="21"/>
       <c r="C3" s="22"/>
       <c r="D3" s="37"/>
-      <c r="E3" s="46"/>
-      <c r="F3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="50"/>
       <c r="G3" s="4"/>
       <c r="H3" s="4"/>
       <c r="I3" s="4"/>
@@ -43049,7 +43049,7 @@
       <c r="C6" s="39"/>
       <c r="D6" s="40"/>
       <c r="E6" s="67"/>
-      <c r="F6" s="63"/>
+      <c r="F6" s="59"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
       <c r="I6" s="4"/>
@@ -43063,8 +43063,8 @@
       <c r="B7" s="25"/>
       <c r="C7" s="39"/>
       <c r="D7" s="21"/>
-      <c r="E7" s="46"/>
-      <c r="F7" s="48"/>
+      <c r="E7" s="48"/>
+      <c r="F7" s="50"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
       <c r="I7" s="4"/>
@@ -43126,7 +43126,7 @@
       <c r="C11" s="32"/>
       <c r="D11" s="21"/>
       <c r="E11" s="62"/>
-      <c r="F11" s="63"/>
+      <c r="F11" s="59"/>
       <c r="G11" s="4"/>
       <c r="H11" s="4"/>
       <c r="I11" s="4"/>
@@ -43140,8 +43140,8 @@
       <c r="B12" s="24"/>
       <c r="C12" s="32"/>
       <c r="D12" s="41"/>
-      <c r="E12" s="46"/>
-      <c r="F12" s="48"/>
+      <c r="E12" s="48"/>
+      <c r="F12" s="50"/>
       <c r="G12" s="4"/>
       <c r="H12" s="4"/>
       <c r="I12" s="4"/>
@@ -43188,7 +43188,7 @@
       <c r="C15" s="21"/>
       <c r="D15" s="40"/>
       <c r="E15" s="67"/>
-      <c r="F15" s="63"/>
+      <c r="F15" s="59"/>
       <c r="G15" s="4"/>
       <c r="H15" s="4"/>
       <c r="I15" s="4"/>
@@ -43202,8 +43202,8 @@
       <c r="B16" s="24"/>
       <c r="C16" s="21"/>
       <c r="D16" s="23"/>
-      <c r="E16" s="46"/>
-      <c r="F16" s="48"/>
+      <c r="E16" s="48"/>
+      <c r="F16" s="50"/>
       <c r="G16" s="4"/>
       <c r="H16" s="4"/>
       <c r="I16" s="4"/>
@@ -43263,7 +43263,7 @@
       <c r="C20" s="21"/>
       <c r="D20" s="21"/>
       <c r="E20" s="62"/>
-      <c r="F20" s="63"/>
+      <c r="F20" s="59"/>
       <c r="G20" s="4"/>
       <c r="H20" s="4"/>
       <c r="I20" s="4"/>
@@ -43277,8 +43277,8 @@
       <c r="B21" s="39"/>
       <c r="C21" s="21"/>
       <c r="D21" s="41"/>
-      <c r="E21" s="46"/>
-      <c r="F21" s="48"/>
+      <c r="E21" s="48"/>
+      <c r="F21" s="50"/>
       <c r="G21" s="4"/>
       <c r="H21" s="4"/>
       <c r="I21" s="4"/>
@@ -43325,7 +43325,7 @@
       <c r="C24" s="39"/>
       <c r="D24" s="44"/>
       <c r="E24" s="67"/>
-      <c r="F24" s="63"/>
+      <c r="F24" s="59"/>
       <c r="G24" s="4"/>
       <c r="H24" s="4"/>
       <c r="I24" s="4"/>
@@ -43339,8 +43339,8 @@
       <c r="B25" s="24"/>
       <c r="C25" s="39"/>
       <c r="D25" s="23"/>
-      <c r="E25" s="46"/>
-      <c r="F25" s="48"/>
+      <c r="E25" s="48"/>
+      <c r="F25" s="50"/>
       <c r="G25" s="4"/>
       <c r="H25" s="4"/>
       <c r="I25" s="4"/>
@@ -43401,7 +43401,7 @@
       <c r="C29" s="32"/>
       <c r="D29" s="21"/>
       <c r="E29" s="62"/>
-      <c r="F29" s="63"/>
+      <c r="F29" s="59"/>
       <c r="G29" s="4"/>
       <c r="H29" s="4"/>
       <c r="I29" s="4"/>
@@ -43415,8 +43415,8 @@
       <c r="B30" s="25"/>
       <c r="C30" s="32"/>
       <c r="D30" s="41"/>
-      <c r="E30" s="46"/>
-      <c r="F30" s="48"/>
+      <c r="E30" s="48"/>
+      <c r="F30" s="50"/>
       <c r="G30" s="4"/>
       <c r="H30" s="4"/>
       <c r="I30" s="4"/>
@@ -43463,7 +43463,7 @@
       <c r="C33" s="22"/>
       <c r="D33" s="40"/>
       <c r="E33" s="67"/>
-      <c r="F33" s="63"/>
+      <c r="F33" s="59"/>
       <c r="G33" s="4"/>
       <c r="H33" s="4"/>
       <c r="I33" s="4"/>
@@ -43477,8 +43477,8 @@
       <c r="B34" s="21"/>
       <c r="C34" s="22"/>
       <c r="D34" s="23"/>
-      <c r="E34" s="46"/>
-      <c r="F34" s="48"/>
+      <c r="E34" s="48"/>
+      <c r="F34" s="50"/>
       <c r="G34" s="4"/>
       <c r="H34" s="4"/>
       <c r="I34" s="4"/>
@@ -57454,6 +57454,17 @@
     </row>
   </sheetData>
   <mergeCells count="23">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="F2:F3"/>
+    <mergeCell ref="D4:D5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="F6:F7"/>
+    <mergeCell ref="C8:C9"/>
+    <mergeCell ref="F11:F12"/>
+    <mergeCell ref="E11:E12"/>
+    <mergeCell ref="D13:D14"/>
+    <mergeCell ref="E15:E16"/>
+    <mergeCell ref="F15:F16"/>
     <mergeCell ref="B18:B19"/>
     <mergeCell ref="F20:F21"/>
     <mergeCell ref="D22:D23"/>
@@ -57466,17 +57477,6 @@
     <mergeCell ref="E29:E30"/>
     <mergeCell ref="F29:F30"/>
     <mergeCell ref="D31:D32"/>
-    <mergeCell ref="C8:C9"/>
-    <mergeCell ref="F11:F12"/>
-    <mergeCell ref="E11:E12"/>
-    <mergeCell ref="D13:D14"/>
-    <mergeCell ref="E15:E16"/>
-    <mergeCell ref="F15:F16"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="F2:F3"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="F6:F7"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
